--- a/Arquivos/Pesquisa_Operacional_09_09_2026.xlsx
+++ b/Arquivos/Pesquisa_Operacional_09_09_2026.xlsx
@@ -8,56 +8,87 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FFE15FC-4F5B-46DC-A269-F7A3BC60044B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FAD8CC-5779-41C0-B4F8-87CD3585223A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
   </bookViews>
   <sheets>
     <sheet name="A1- Capitão Caverna" sheetId="3" r:id="rId1"/>
+    <sheet name="A2 - Beta Ltda" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$B$3:$D$3</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$B$2:$D$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$10</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$E$8:$E$12</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$11</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$12</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$8</definedName>
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$9</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$B$5</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$B$4</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$10</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$F$8:$F$12</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$11</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$12</definedName>
     <definedName name="solver_rhs4" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$8</definedName>
     <definedName name="solver_rhs5" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$9</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -151,8 +182,91 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Fatec</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{147DECFE-ACBA-499A-9A56-08E02ACEF029}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fatec:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>O valor das variáveis será preenchido pelo Solver. O Solver é acessado na aba: Dados &gt; Solver.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{CD76A702-1645-4429-8CF9-DCF41C72DF61}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Informar lucro de cada variável.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{73FFCC2A-0C9D-43FF-8D91-A88746FED977}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Restrição 1 * Variável 1 + Restrição 2 * Variável 2 + Restrição 3 * Variável 3.
+Linhas seguintes: Travar as variáveis e seguir com as restrições 2,3,4...</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
   <si>
     <t>Quantidade:</t>
   </si>
@@ -203,6 +317,30 @@
   </si>
   <si>
     <t>R5 - ARCAS</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>R1 - HT</t>
+  </si>
+  <si>
+    <t>R2 - HM</t>
+  </si>
+  <si>
+    <t>R3 - DEMANDA P1</t>
+  </si>
+  <si>
+    <t>R3 - DEMANDA P2</t>
+  </si>
+  <si>
+    <t>R3 - DEMANDA P3</t>
   </si>
 </sst>
 </file>
@@ -300,11 +438,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -313,6 +454,11 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bom" xfId="1" builtinId="26"/>
@@ -507,6 +653,114 @@
         <a:xfrm>
           <a:off x="542925" y="3095625"/>
           <a:ext cx="3914775" cy="4106073"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>391614</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>189416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>306119</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>145941</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagem 6" descr="lindo betta peixe em transparente fundo 19988494 PNG">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2E4DCF8-0139-4224-8F12-6BEE8798FA0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="12807" t="6518" r="14539"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="20169152">
+          <a:off x="5801814" y="379916"/>
+          <a:ext cx="2352905" cy="2242525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>115858</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagem 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D67B0F26-5574-4A79-8E44-1EE4867696B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8220075" y="200025"/>
+          <a:ext cx="6781800" cy="4487833"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -828,13 +1082,13 @@
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -842,13 +1096,13 @@
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="7">
         <v>4</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
         <v>4</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="7">
         <v>2</v>
       </c>
     </row>
@@ -856,13 +1110,13 @@
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="10">
         <v>50</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>70</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <v>100</v>
       </c>
     </row>
@@ -870,7 +1124,7 @@
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <f>B4*B3+C4*C3+D4*D3</f>
         <v>680</v>
       </c>
@@ -878,25 +1132,25 @@
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="L6" s="8"/>
+      <c r="L6" s="9"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -913,7 +1167,7 @@
       <c r="D8" s="3">
         <v>0</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <f>B8*B3</f>
         <v>4</v>
       </c>
@@ -934,11 +1188,11 @@
       <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <f>B9*B3+C9*C3+D9*D3</f>
         <v>18</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <v>18</v>
       </c>
     </row>
@@ -955,7 +1209,7 @@
       <c r="D10" s="3">
         <v>1</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <f>B10*B3+C10*C3+D10*D3</f>
         <v>10</v>
       </c>
@@ -967,20 +1221,20 @@
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <v>0</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
         <v>1</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="6">
         <v>0</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <f>C11*C3</f>
         <v>4</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="6">
         <v>8</v>
       </c>
     </row>
@@ -988,20 +1242,20 @@
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="6">
         <v>0</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <v>0</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="6">
         <v>1</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <f>D12*D3</f>
         <v>2</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <v>3</v>
       </c>
     </row>
@@ -1013,6 +1267,201 @@
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8733FB85-6A8E-4387-BA98-C55875E46742}">
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12">
+        <v>280</v>
+      </c>
+      <c r="C2" s="12">
+        <v>600</v>
+      </c>
+      <c r="D2" s="12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13">
+        <v>2100</v>
+      </c>
+      <c r="C3" s="13">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="13">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="13">
+        <f>B3*B2+C3*C2+D3*D2</f>
+        <v>1380000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4">
+        <f>B8*B2+C8*C2+D8*D2</f>
+        <v>4800</v>
+      </c>
+      <c r="F8" s="11">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="5">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4">
+        <f>B9*B2+C9*C2+D9*D2</f>
+        <v>7200</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f>B10*B2</f>
+        <v>280</v>
+      </c>
+      <c r="F10" s="5">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f>C11*C2</f>
+        <v>600</v>
+      </c>
+      <c r="F11" s="5">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <f>D12*D2</f>
+        <v>120</v>
+      </c>
+      <c r="F12" s="5">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/Arquivos/Pesquisa_Operacional_09_09_2026.xlsx
+++ b/Arquivos/Pesquisa_Operacional_09_09_2026.xlsx
@@ -8,87 +8,121 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FAD8CC-5779-41C0-B4F8-87CD3585223A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30152FF9-665C-405E-8F51-82C7F6D7107D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
   </bookViews>
   <sheets>
     <sheet name="A1- Capitão Caverna" sheetId="3" r:id="rId1"/>
     <sheet name="A2 - Beta Ltda" sheetId="4" r:id="rId2"/>
+    <sheet name="A3- Alimentação" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$B$3:$D$3</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$B$2:$D$2</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'A3- Alimentação'!$B$2:$C$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$10</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$E$8:$E$12</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'A3- Alimentação'!$D$8</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$11</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'A3- Alimentação'!$D$9</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$12</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$8</definedName>
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$9</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">5</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$B$5</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$B$4</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'A3- Alimentação'!$B$4</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$10</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$F$8:$F$12</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'A3- Alimentação'!$E$8</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$11</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">'A3- Alimentação'!$E$9</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$12</definedName>
     <definedName name="solver_rhs4" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$8</definedName>
     <definedName name="solver_rhs5" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$9</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -265,8 +299,91 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Fatec</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{FDC8E970-32EF-4033-87E5-D2194E9FF602}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fatec:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>O valor das variáveis será preenchido pelo Solver. O Solver é acessado na aba: Dados &gt; Solver.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{8547ACF3-81E6-402E-A504-EC944ABA5544}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Informar lucro de cada variável.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{A5591A82-A2D5-4A66-9E94-16ACFA91DC7C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Restrição 1 * Variável 1 + Restrição 2 * Variável 2 + Restrição 3 * Variável 3.
+Linhas seguintes: Travar as variáveis e seguir com as restrições 2,3,4...</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Quantidade:</t>
   </si>
@@ -292,6 +409,9 @@
     <t>Variáveis:</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Função Objetivo:</t>
   </si>
   <si>
@@ -341,6 +461,18 @@
   </si>
   <si>
     <t>R3 - DEMANDA P3</t>
+  </si>
+  <si>
+    <t>MINIMIZAR</t>
+  </si>
+  <si>
+    <t>R2 - PROTEINA</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>R1 - VITAMINA</t>
   </si>
 </sst>
 </file>
@@ -438,7 +570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -459,6 +591,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bom" xfId="1" builtinId="26"/>
@@ -761,6 +894,99 @@
         <a:xfrm>
           <a:off x="8220075" y="200025"/>
           <a:ext cx="6781800" cy="4487833"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>19049</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>7180</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B8614AF-885F-4AE8-A43B-D33981AD0A12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3876674" y="123825"/>
+          <a:ext cx="2505075" cy="2359855"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>305841</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>48294</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D8F40C9-DF99-4F6C-9A4C-C75576CAECD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6457950" y="209550"/>
+          <a:ext cx="7459116" cy="4791744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1083,13 +1309,13 @@
         <v>7</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1122,7 +1348,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="8">
         <f>B4*B3+C4*C3+D4*D3</f>
@@ -1139,13 +1365,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -1156,7 +1382,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -1177,7 +1403,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
@@ -1198,7 +1424,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3">
         <v>1</v>
@@ -1219,7 +1445,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="6">
         <v>0</v>
@@ -1240,7 +1466,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="6">
         <v>0</v>
@@ -1293,13 +1519,13 @@
         <v>7</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1332,7 +1558,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="13">
         <f>B3*B2+C3*C2+D3*D2</f>
@@ -1344,13 +1570,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>4</v>
@@ -1361,7 +1587,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5">
         <v>6</v>
@@ -1382,7 +1608,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="5">
         <v>12</v>
@@ -1403,7 +1629,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
@@ -1424,7 +1650,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="5">
         <v>0</v>
@@ -1445,7 +1671,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5">
         <v>0</v>
@@ -1462,6 +1688,118 @@
       </c>
       <c r="F12" s="5">
         <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26DA9860-C23E-47A9-943B-DBFD30E3A4E6}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12">
+        <v>0</v>
+      </c>
+      <c r="C2" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="13">
+        <v>3</v>
+      </c>
+      <c r="C3" s="13">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="14">
+        <f>B3*B2+C3*C2</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8</v>
+      </c>
+      <c r="D8" s="4">
+        <f>B8*B2+C8*C2</f>
+        <v>48</v>
+      </c>
+      <c r="E8" s="5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4">
+        <f>B9*B2+C9*C2</f>
+        <v>36</v>
+      </c>
+      <c r="E9" s="5">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Arquivos/Pesquisa_Operacional_09_09_2026.xlsx
+++ b/Arquivos/Pesquisa_Operacional_09_09_2026.xlsx
@@ -8,37 +8,45 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30152FF9-665C-405E-8F51-82C7F6D7107D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2222488C-A642-422C-BAD5-25C49839A40F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="3" xr2:uid="{759A8800-CD47-4849-AA2E-61C2ECE26B63}"/>
   </bookViews>
   <sheets>
     <sheet name="A1- Capitão Caverna" sheetId="3" r:id="rId1"/>
     <sheet name="A2 - Beta Ltda" sheetId="4" r:id="rId2"/>
     <sheet name="A3- Alimentação" sheetId="5" r:id="rId3"/>
+    <sheet name="A4-  Jardim" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$B$3:$D$3</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$B$2:$D$2</definedName>
     <definedName name="solver_adj" localSheetId="2" hidden="1">'A3- Alimentação'!$B$2:$C$2</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">'A4-  Jardim'!$B$2:$C$2</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$10</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$E$8:$E$12</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">'A3- Alimentação'!$D$8</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'A4-  Jardim'!$D$7:$D$9</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$11</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'A3- Alimentação'!$D$9</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$E$12</definedName>
@@ -47,39 +55,51 @@
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">5</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$B$5</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$B$4</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">'A3- Alimentação'!$B$4</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">'A4-  Jardim'!$B$4</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
@@ -88,6 +108,7 @@
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$10</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'A2 - Beta Ltda'!$F$8:$F$12</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">'A3- Alimentação'!$E$8</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">'A4-  Jardim'!$E$7:$E$9</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$11</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">'A3- Alimentação'!$E$9</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">'A1- Capitão Caverna'!$F$12</definedName>
@@ -96,33 +117,43 @@
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -382,8 +413,91 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Fatec</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{6F411FB0-3393-4D44-B310-E393B8832E6D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fatec:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>O valor das variáveis será preenchido pelo Solver. O Solver é acessado na aba: Dados &gt; Solver.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{93D2B0D8-094B-4BEF-8E47-FDE3E93C2753}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Informar lucro de cada variável.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{304A0FA9-F67C-4BB9-B5EC-E6C5C15410BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Restrição 1 * Variável 1 + Restrição 2 * Variável 2 + Restrição 3 * Variável 3.
+Linhas seguintes: Travar as variáveis e seguir com as restrições 2,3,4...</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="34">
   <si>
     <t>Quantidade:</t>
   </si>
@@ -473,6 +587,18 @@
   </si>
   <si>
     <t>R1 - VITAMINA</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>R1 - A</t>
+  </si>
+  <si>
+    <t>R2 -  B</t>
+  </si>
+  <si>
+    <t>R3 - C</t>
   </si>
 </sst>
 </file>
@@ -480,7 +606,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -570,7 +696,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -583,15 +709,17 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bom" xfId="1" builtinId="26"/>
@@ -998,6 +1126,116 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>58210</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78D3435C-B859-414D-A528-2B9B7B4831C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6705600" y="190500"/>
+          <a:ext cx="7592485" cy="4686954"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>105429</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3" descr="17 ideias de Smilinguido frase bíblica | smilinguido, frases bonitas  evangelicas, imagens do smilinguido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F336A60-440E-4D14-8254-DB286466A2E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4133850" y="180975"/>
+          <a:ext cx="2647950" cy="2972454"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -1807,4 +2045,134 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2AD526E-FE79-4EF8-BBD7-1576CADA9B99}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15">
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="C2" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="3">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="16">
+        <f>SUMPRODUCT(B2:C2,B3:C3)</f>
+        <v>13</v>
+      </c>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4">
+        <f>SUMPRODUCT(B7:C7,B2:C2)</f>
+        <v>10</v>
+      </c>
+      <c r="E7" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <f>SUMPRODUCT(B8:C8,B2:C2)</f>
+        <v>12</v>
+      </c>
+      <c r="E8" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="4">
+        <f>SUMPRODUCT(B9:C9,B2:C2)</f>
+        <v>21</v>
+      </c>
+      <c r="E9" s="5">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>